--- a/TestData/Transfer_TestData.xlsx
+++ b/TestData/Transfer_TestData.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="33.83" customWidth="1" style="1" min="1" max="1"/>
@@ -762,29 +762,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Wallet transfer to a recipient by mobile</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>lawma195.infinity@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>855 965321152</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>A transfer aimed at the account making it</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
         </is>
       </c>
     </row>
